--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
     </row>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -439,16 +439,8 @@
           <t>AZAFRAN CDAD TIERRABUENA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -456,16 +448,8 @@
           <t>COUNTRY WOODS</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -439,8 +439,16 @@
           <t>AZAFRAN CDAD TIERRABUENA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -448,8 +456,16 @@
           <t>COUNTRY WOODS</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,142 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>COUNTRY PARK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SKY TOWER</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PANORAMIK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ALCALA GRAN RESERVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE AURORA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE SOLEIL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TERRAZA DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BOSQUES DEL HATO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,7 +526,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -600,6 +600,23 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE MONTEVISTA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
     </row>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
     </row>
